--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486815_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486815_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4007</v>
+        <v>5.7302</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6623</v>
+        <v>5.2898</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.4404</v>
       </c>
       <c r="G2" t="n">
         <v>3.5438</v>
@@ -610,13 +610,13 @@
         <v>0.5792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.05</v>
+        <v>0.3795</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6347</v>
+        <v>-0.0072</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6846</v>
+        <v>0.3866</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.025</v>
+        <v>3.3941</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7362</v>
+        <v>2.9468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2888</v>
+        <v>0.4472</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5394</v>
+        <v>4.0899</v>
       </c>
       <c r="H3" t="n">
-        <v>1.648</v>
+        <v>3.4547</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1085</v>
+        <v>0.6353</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4092</v>
+        <v>2.9672</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7175</v>
+        <v>2.3523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6918</v>
+        <v>0.615</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8698</v>
+        <v>1.1227</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.06950000000000001</v>
+        <v>1.1024</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8003</v>
+        <v>0.0203</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5792</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7945</v>
+        <v>0.0072</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0279</v>
+        <v>-0.3519</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8224</v>
+        <v>0.3592</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2703</v>
+        <v>1.2277</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5133</v>
+        <v>2.4554</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.243</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0231</v>
+        <v>2.8628</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5262</v>
+        <v>2.1976</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4969</v>
+        <v>0.6652</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0899</v>
+        <v>2.0103</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4547</v>
+        <v>0.2129</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6353</v>
+        <v>1.7973</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9672</v>
+        <v>2.1978</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3523</v>
+        <v>0.5587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.615</v>
+        <v>1.6391</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1227</v>
+        <v>-0.1876</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1024</v>
+        <v>-0.3458</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0203</v>
+        <v>0.1582</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3637</v>
+        <v>0.3312</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7725</v>
+        <v>-0.0002</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4088</v>
+        <v>0.3314</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2277</v>
+        <v>0.3282</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6414</v>
+        <v>2.6305</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0758</v>
+        <v>2.6397</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5656</v>
+        <v>-0.0092</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0825</v>
+        <v>1.5394</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8896</v>
+        <v>1.648</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8071</v>
+        <v>-0.1085</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3948</v>
+        <v>2.4092</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9599</v>
+        <v>1.7175</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5651</v>
+        <v>0.6918</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3122</v>
+        <v>-0.8698</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0703</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.242</v>
+        <v>-0.8003</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9654</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>1.953</v>
+        <v>0.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2682</v>
+        <v>-0.1244</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6847</v>
+        <v>0.5244</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5712</v>
+        <v>1.2703</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5712</v>
+        <v>1.5133</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2394</v>
+        <v>1.723</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6735</v>
+        <v>1.2071</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5659</v>
+        <v>0.5159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0103</v>
+        <v>1.0825</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2129</v>
+        <v>1.8896</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7973</v>
+        <v>-0.8071</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1978</v>
+        <v>1.3948</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5587</v>
+        <v>1.9599</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6391</v>
+        <v>-0.5651</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1876</v>
+        <v>-0.3122</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3458</v>
+        <v>-0.0703</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1582</v>
+        <v>-0.242</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R6" t="n">
         <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2922</v>
+        <v>1.0346</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5243</v>
+        <v>0.3996</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2321</v>
+        <v>0.6351</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3282</v>
+        <v>0.5712</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3996</v>
+        <v>0.5285</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2831</v>
+        <v>0.0392</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1165</v>
+        <v>0.4893</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0339</v>
+        <v>-0.1059</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4273</v>
+        <v>-0.0968</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3934</v>
+        <v>-0.0091</v>
       </c>
       <c r="J7" t="n">
-        <v>1.359</v>
+        <v>0.1635</v>
       </c>
       <c r="K7" t="n">
-        <v>1.359</v>
+        <v>0.0414</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1221</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3251</v>
+        <v>-0.2693</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0682</v>
+        <v>-0.1382</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3934</v>
+        <v>-0.1311</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3311</v>
+        <v>0.2482</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0825</v>
+        <v>-0.1242</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2486</v>
+        <v>0.3725</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2417</v>
+        <v>0.1997</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2228</v>
+        <v>0.0832</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4645</v>
+        <v>0.1165</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1059</v>
+        <v>1.0339</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0968</v>
+        <v>1.4273</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0091</v>
+        <v>-0.3934</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1635</v>
+        <v>1.359</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0414</v>
+        <v>1.359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2693</v>
+        <v>-0.3251</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1382</v>
+        <v>0.0682</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1311</v>
+        <v>-0.3934</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0386</v>
+        <v>0.1312</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3863</v>
+        <v>-0.1174</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3476</v>
+        <v>0.2486</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9182</v>
+        <v>-0.3527</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3627</v>
+        <v>-0.0455</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5555</v>
+        <v>-0.3072</v>
       </c>
       <c r="G9" t="n">
         <v>1.2013</v>
@@ -1156,13 +1156,13 @@
         <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1308</v>
+        <v>-0.5653</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7725</v>
+        <v>-0.4553</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3583</v>
+        <v>-0.1099</v>
       </c>
       <c r="V9" t="n">
         <v>0.9421</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3607</v>
+        <v>-1.4446</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2368</v>
+        <v>-1.6435</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1239</v>
+        <v>0.199</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9342</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7667</v>
+        <v>0.6827</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8547</v>
+        <v>0.4479</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.2348</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2301</v>
+        <v>-4.706</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1673</v>
+        <v>-3.6432</v>
       </c>
       <c r="F11" t="n">
         <v>-1.0628</v>
@@ -1312,10 +1312,10 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1379</v>
+        <v>0.3862</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4691</v>
+        <v>0.0549</v>
       </c>
       <c r="U11" t="n">
         <v>0.3312</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.461899999999998</v>
+        <v>10.5655</v>
       </c>
       <c r="E12" t="n">
-        <v>7.9675</v>
+        <v>9.071199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4944</v>
+        <v>1.4943</v>
       </c>
       <c r="G12" t="n">
         <v>10.3422</v>
@@ -1390,13 +1390,13 @@
         <v>3.8616</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9321</v>
+        <v>3.0355</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3819</v>
+        <v>-0.2781999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3137</v>
+        <v>3.3139</v>
       </c>
       <c r="V12" t="n">
         <v>4.9107</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6265</v>
+        <v>5.7478</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6938</v>
+        <v>5.9007</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0673</v>
+        <v>-0.1529</v>
       </c>
       <c r="G13" t="n">
         <v>2.4016</v>
@@ -1468,13 +1468,13 @@
         <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1765</v>
+        <v>-0.0553</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6901</v>
+        <v>-0.4832</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5135</v>
+        <v>0.428</v>
       </c>
       <c r="V13" t="n">
         <v>1.4707</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9229</v>
+        <v>2.4911</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7875</v>
+        <v>1.9943</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1354</v>
+        <v>0.4968</v>
       </c>
       <c r="G14" t="n">
         <v>0.7865</v>
@@ -1546,13 +1546,13 @@
         <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2579</v>
+        <v>-0.6896</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1036</v>
+        <v>-0.8968</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1542</v>
+        <v>0.2072</v>
       </c>
       <c r="V14" t="n">
         <v>0.6565</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2965</v>
+        <v>0.1793</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7429</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4464</v>
+        <v>0.1793</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4709</v>
+        <v>0.1379</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3789</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0919</v>
+        <v>0.1379</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3645</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9319</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5674</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8354</v>
+        <v>0.1379</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3109</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5245</v>
+        <v>0.1379</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0297</v>
+        <v>0.0414</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3784</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6513</v>
+        <v>0.0414</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1975</v>
+        <v>0.1066</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3006</v>
+        <v>-0.1131</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1031</v>
+        <v>0.2197</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5343</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1872</v>
+        <v>0.0963</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2753</v>
+        <v>-0.1384</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0881</v>
+        <v>0.2347</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1545</v>
+        <v>-1.168</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.5018</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1545</v>
+        <v>-1.6698</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1379</v>
+        <v>-1.4709</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.3789</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1379</v>
+        <v>-1.0919</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.3645</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.9319</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.5674</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1379</v>
+        <v>-1.8354</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.3109</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1379</v>
+        <v>-0.5245</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0166</v>
+        <v>0.5651</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1373</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0166</v>
+        <v>0.4278</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4483</v>
+        <v>-1.3863</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2946</v>
+        <v>-1.9844</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8464</v>
+        <v>0.5981</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7116</v>
@@ -1858,13 +1858,13 @@
         <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1654</v>
+        <v>-0.1035</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6622</v>
+        <v>-0.3519</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4968</v>
+        <v>0.2484</v>
       </c>
       <c r="V18" t="n">
         <v>0.0426</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.282</v>
+        <v>-1.689</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5259</v>
+        <v>0.7328</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.808</v>
+        <v>-2.4218</v>
       </c>
       <c r="G19" t="n">
         <v>0.1735</v>
@@ -1936,13 +1936,13 @@
         <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3517</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9381</v>
+        <v>-0.7313</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4136</v>
+        <v>-0.0274</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4554</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7894</v>
+        <v>-1.8916</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9529</v>
+        <v>-1.2289</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8365</v>
+        <v>-0.6627</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2777</v>
@@ -2014,13 +2014,13 @@
         <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1255</v>
+        <v>-0.2278</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9381</v>
+        <v>-0.2141</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1874</v>
+        <v>-0.0136</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5369</v>
+        <v>-3.3368</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2012</v>
+        <v>-0.9292</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3357</v>
+        <v>-2.4076</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3123</v>
+        <v>-1.8771</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5451</v>
+        <v>-2.4965</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2328</v>
+        <v>0.6194</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2262</v>
+        <v>-1.3316</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1448</v>
+        <v>-1.2548</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0814</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5385</v>
+        <v>-0.5454</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6899</v>
+        <v>-1.2417</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1514</v>
+        <v>0.6962</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6454</v>
+        <v>0.1308</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4966</v>
+        <v>0.1168</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1488</v>
+        <v>0.014</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>-2.1698</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6719</v>
+        <v>-3.3742</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2394</v>
+        <v>-2.2012</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4324</v>
+        <v>-1.173</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8771</v>
+        <v>-0.3123</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4965</v>
+        <v>-0.5451</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6194</v>
+        <v>0.2328</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3316</v>
+        <v>0.2262</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2548</v>
+        <v>0.1448</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.0814</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5454</v>
+        <v>-0.5385</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2417</v>
+        <v>-0.6899</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6962</v>
+        <v>0.1514</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5792</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R22" t="n">
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2043</v>
+        <v>-0.4827</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1934</v>
+        <v>-0.4966</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0109</v>
+        <v>0.014</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1698</v>
+        <v>-1.2277</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4554</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9312</v>
+        <v>-4.4512</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.857</v>
+        <v>-4.1673</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0742</v>
+        <v>-0.2839</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6578</v>
@@ -2248,13 +2248,13 @@
         <v>1.9308</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7613</v>
+        <v>0.2413</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0546</v>
+        <v>-0.2557</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7067</v>
+        <v>0.4969</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.4618</v>
+        <v>-8.772300000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4944</v>
+        <v>-1.4945</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.967300000000001</v>
+        <v>-7.2778</v>
       </c>
       <c r="G24" t="n">
         <v>-10.3422</v>
@@ -2326,13 +2326,13 @@
         <v>11.5846</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9319</v>
+        <v>-1.2426</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.3138</v>
+        <v>-3.3139</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3819</v>
+        <v>2.0714</v>
       </c>
       <c r="V24" t="n">
         <v>-4.9108</v>
